--- a/backend/seeded_templates/Seeded_Services_Import.xlsx
+++ b/backend/seeded_templates/Seeded_Services_Import.xlsx
@@ -552,7 +552,7 @@
         <v>https://images.unsplash.com/photo-1581092918056-0c4c3acd3789?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="Y2" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +569,7 @@
         <v>Custom fabrication, cutting, fit-up, and certified radiographic-grade welding of heavy industrial trusses, columns, conveyor galleries, and storage silos according to structural drawings.</v>
       </c>
       <c r="E3" t="str">
-        <v>PER_UNIT</v>
+        <v>PER_PROJECT</v>
       </c>
       <c r="F3">
         <v>19500</v>
@@ -646,7 +646,7 @@
         <v>Precision civil engineering services for casting vibration-damped concrete equipment foundations, crusher beds, compressor plinths, and heavy crane track foundations.</v>
       </c>
       <c r="E4" t="str">
-        <v>PROJECT</v>
+        <v>PER_PROJECT</v>
       </c>
       <c r="F4">
         <v>135000</v>
@@ -706,7 +706,7 @@
         <v>https://images.unsplash.com/photo-1486406146926-c627a92ad1ab?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="Y4" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v>Comprehensive third-party NDT quality evaluation of pressure vessels, heavy weld joints, boiler tubes, crane hooks, and forged shafts to detect internal flaws and surface fissures.</v>
       </c>
       <c r="E5" t="str">
-        <v>PER_UNIT</v>
+        <v>DAILY</v>
       </c>
       <c r="F5">
         <v>28000</v>
@@ -800,7 +800,7 @@
         <v>Full-time operational management and environmental compliance monitoring of industrial effluent and sewage treatment plants to achieve zero liquid discharge (ZLD).</v>
       </c>
       <c r="E6" t="str">
-        <v>RETAINER</v>
+        <v>MONTHLY</v>
       </c>
       <c r="F6">
         <v>68000</v>
@@ -860,7 +860,7 @@
         <v>https://images.unsplash.com/photo-1565043666747-69f6646db940?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="Y6" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="7">
@@ -877,7 +877,7 @@
         <v>Turnkey industrial rigging, base leveling, anchor grouting, and precision laser shaft alignment of heavy rotating equipment: ball mills, crushers, turbo-blowers, and multistage pumps.</v>
       </c>
       <c r="E7" t="str">
-        <v>PROJECT</v>
+        <v>PER_PROJECT</v>
       </c>
       <c r="F7">
         <v>88000</v>
@@ -954,7 +954,7 @@
         <v>Statutory annual safety inspection, brake shoe relining, wire rope ultrasonic flaw testing, deflection measurement, and full 125% proof load testing under Factories Act Form 9.</v>
       </c>
       <c r="E8" t="str">
-        <v>PER_UNIT</v>
+        <v>FIXED</v>
       </c>
       <c r="F8">
         <v>38000</v>
@@ -1014,7 +1014,7 @@
         <v>https://images.unsplash.com/photo-1586528116311-ad8dd3c8310d?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="Y8" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="9">
@@ -1031,7 +1031,7 @@
         <v>Complete engineering, procurement, and construction of industrial rooftop solar system with high-efficiency Tier-1 mono PERC modules, string inverters, and net-metering approval.</v>
       </c>
       <c r="E9" t="str">
-        <v>PROJECT</v>
+        <v>PER_PROJECT</v>
       </c>
       <c r="F9">
         <v>3850000</v>
@@ -1108,7 +1108,7 @@
         <v>Contract logistics and bulk transport management for coal, iron ore, steel billets, and finished machinery across major industrial corridors with GPS live-tracked fleet.</v>
       </c>
       <c r="E10" t="str">
-        <v>PER_UNIT</v>
+        <v>DAILY</v>
       </c>
       <c r="F10">
         <v>1250</v>
@@ -1168,7 +1168,7 @@
         <v>https://images.unsplash.com/photo-1586528116311-ad8dd3c8310d?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="Y10" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="11">
